--- a/new/261025.xlsx
+++ b/new/261025.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E199AE37-81C0-4294-A2E2-EC17CC64E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DADAF4-1836-433B-8FAB-192DD669C7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10300" yWindow="4040" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="SheetX" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="SheetX" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Tauber: Also, wir haben uns darum gekümmert, dass wir als CDU – und dazu dienen ja auch die Deutschlandkongresse, die derzeit mit der bayerischen Schwester zusammen stattfinden – programmatisch auf der Höhe der Zeit bleiben.
 Wir haben für die Partei selbst eine Parteireform auf den Weg gebracht – " Meine CDU 2017" –, wo es dann auch um organisatorische und strukturelle Fragen geht, damit wir als Volkspartei nah bei den Menschen bleiben.
@@ -422,130 +423,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Küpper: Auch Sie wurden ja mit diesem schweren Attentat, das auf Sie verübt wurde, ja ein Stück weit für Merkels Flüchtlingspolitik verantwortlich gemacht – so war es zumindest, so hat der Attentäter das damals ein Stück weit begründet.
-Haben Sie für sich diese Verbindung auch schon einmal herstellt, dieses """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir schaffen das"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" und dieses Attentat dann letztendlich?
-Reker: Also, in den Vorstellungen des Täters ist es so gewesen.
-Aber ich habe ja vor diesem Attentat keine flammenden Reden zur Flüchtlingsunterbringung gehalten, sondern ich habe meine Aufgabe erledigt.
-Küpper: Als Sozialdezernentin.
-Reker: Als Sozialdezernentin – nicht mehr und nicht weniger.
-Und ich haben eben immer offen und ehrlich darauf hingewiesen, dass ich vorschlage, das zu akzeptieren und mit dieser Situation zu leben und sich dem positiv zu nähern.
-Aber die Reflektion des Täters ist sowieso für mich völlig schleierhaft.
-Küpper: Wie präsent ist dieses Attentat bei Ihnen noch im Alltag?
-Reker: Es ist jeden Tag präsent.
-Ich leide da nicht drunter, ich habe auch keine Zeit, da lange drüber nachzudenken, aber ich werde eben offen auch darauf angesprochen und mittlerweile kann ich damit wirklich ganz gut umgehen.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir müssen eine angemessene, ruhige, argumentative politische Kultur pflegen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Bei Ihrem ersten öffentlichen Auftritt nach diesem Attentat und auch nach der Wahl, bei der Verleihung des Heinrich-Böll-Preises an die Schriftstellerin Herta Müller, da hat diese gesagt: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wenn Worte, wie 'Volksverräter' und 'Lügenpresse' langegenug spazieren gehen, geht auch mal ein Messer spazieren."""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir erleben es ja in Deutschland immer noch tagtäglich, was für eine teilweise rohe und aufgeheizte Debatte wir führen, sei es in den sogenannten """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Sozialen Netzwerken"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , aber auch anderswo.
-Wird genug getan, diesem Satz, den Herta Müller da ja gesagt hat, den umzusetzen, dem Einhalt zu gebieten, dieser Verrohung teilweise der Diskussion?
-Reker: Der Satz von Herta Müller, dass erst Parolen spazieren gehen und dann Messer – ich sage es mal jetzt sinngemäß –, den zitiere ich oft, weil ich glaube, dass der genau stimmt.
-Und diese politische Kultur der Auseinandersetzung, die führt – davon bin ich zutiefst überzeugt – dazu, dass dann auch es zu solchen Tätlichkeiten kommt.
-Weil man muss sich ja mal vorstellen, es gehört ja eine gewisse Überwindung dazu, jemandem ein Messer irgendwie in den Körper zu stechen.
-Das kommt nicht von selbst und da muss eben ein Hasspotenzial aufgebaut sein, was auch nicht von selbst entsteht.
-Und wenn das immer wieder unterstützt wird durch Parolen, durch Menschen, die die Situation befeuern, um ihre eigenen Interessen zu schüren, um ihr Süppchen kochen zu wollen – ohne eine Alternative allerdings zu haben –, dann wird das gefährlich für uns alle.
-Und deswegen trete ich immer dafür ein, dass wir auch eine angemessene, ruhige, argumentative politische Kultur pflegen.
-Küpper: Was kann man da tun?
-Sie sind Juristin.
-Reichen da Gesetze oder ist das eher eine gesellschaftliche Sache?
-Reker: Es ist eine gesellschaftliche Sache, es ist nicht alles justiziabel, was da passiert, das sehen wir ja an Demonstrationen und an Gewalt in den Demonstrationen.
-Ich glaube, dass man da ganz früh ansetzen muss.
-Und ich glaube auch, dass diese Flüchtlingsbewegung, die jetzt eingetreten sind, eine Chance ist für Kinder, in der Schule sich schon damit zu beschäftigen.
-Das erlebe ich nämlich, dass schon Schulkinder lernen, wo kommen die anderen her, warum sind die da – das ist auch eine Chance.
-Küpper: Dann noch kurz: Das Gericht hat den Attentäter zu 14 Jahren Freiheitsstrafe verurteilt, allerdings niederer Beweggründe dabei verneint, obwohl es ja klar eine rechtsextreme Gewaltbereitschaft damals gab.
-Das ist ein – kann man, glaube ich, so sagen – recht mildes Urteil gewesen.
-Welche Botschaft geht davon aus?
-Reker: Also, ich konnte das nicht nachvollziehen, dass man die niedrigen Beweggründe nicht angenommen hat.
-Ich muss Ihnen sagen, ich finde das jetzt für mich persönlich nicht wichtig, ob der Attentäter zu 14 oder 15 Jahren verurteilt wird.
-Küpper: Aber wir sprechen über die gesellschaftliche ...
-Reker: Also, ich kann einfach nicht nachvollziehen, wie jemand aus rechter Gewalt töten will und das soll kein niedriger Beweggrund sein.
-Und deswegen habe ich auch so eine Sorge vor der Revision, die ich niemals eingelegt hätte.
-Ich stelle mir mir Grausen vor, dass ein Bundesgericht bestätigt, dass man aus rechter Gewalt einen Mordversuch macht und das keine niedrigen Beweggründe sein sollen.
-Ich bin mal sehr gespannt.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es sind viele positive Dinge übrig geblieben von der Silvesternacht"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Sie hören das Interview der Woche im Deutschlandfunk.
-Zu Gast ist Henriette Reker, die Oberbürgermeisterin der Stadt Köln.
-Frau Reker, am Anfang des Jahres, da stand die Silvesternacht – die ist mittlerweile ein geflügeltes Wort, gerade im Kontext von Köln.
-Wie viel von dieser Silvesternacht ist in Ihrer Stadt noch zu spüren?
-Reker: Es ist ganz viel Positives von dieser Silvesternacht zu spüren.
-Küpper: Was?
-Reker: Die Silvesternacht hat mich ja dazu gebracht, ein """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Stärkungsmodell Sicherheit"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" zu konstruieren.
-Eine Zusammenarbeit, eine institutionelle Zusammenarbeit mit der Polizei, die es in dieser Form noch nie gegeben hat in Köln.
-Und es hat auch einen stärkeren Personaleinsatz gegeben für die Polizei, die Stadt hat 100 Ordnungskräfte mehr auf der Straße.
-Es sind viele positive Dinge übrig geblieben von der Silvesternacht.
-Küpper: Das Image hat nicht gelitten?
-Reker: Das Image hat gelitten.
-Aber ich glaube, das Schlimmste daran, an Silvester, war wirklich das Trauma der überfallenen Frauen, dass sicherlich nicht nach wenigen Monaten ausgestanden ist.
-Denen galt auch mein erster Gedanke.
-Aber mitzuweinen hat da wenig Zweck.
-Da geht es darum zu handeln und solche Dinge in der Zukunft zu verhindern.
-Das habe ich getan.
-Küpper: Dennoch muss die Sache auch aufgearbeitet werden, das haben Sie ja auch gerade gesagt.
-Wenn man da auf die juristische Seite guckt, ich habe diese Woche mal beim Amtsgericht nachgefragt, da sind jetzt 15 Urteile gefällt worden.
-Angesichts der Tatsache, der hohen Zahl von Anzeigen – über 1.000 – und Anzahl der jetzt über acht Monate, die verstrichen sind seitdem, wie zufrieden sind Sie mit dem?
-Reker: Gar nicht zufrieden.
-Gar nicht zufrieden.
-Aber das war ja zu erwarten, dass es sehr schwerfallen wird, dass die Frauen dann diese Täter wiedererkennen.
-Also, das geht im Einzelfall, aber ganz überwiegend geht es eben nicht.
-Und das ist daran wirklich schlimm, dass die Männer nicht zur Rechenschaft gezogen werden können.
-Küpper: Das heißt, es war klar, dass diese Erwartungshaltung, die es da ein stückweit gab, automatisch enttäuscht werden musste?
-Reker: Ich habe das befürchtet, ja.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es wird hier Wahlkampf mit einem schrecklichen Vorfall in unserer Stadt gemacht"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Wenn wir auf die politische Aufarbeitung gucken, da gibt es im Düsseldorfer Landtag einen parlamentarischen Untersuchungsausschuss, vor dem Sie ja auch schon als Zeugin ausgesagt haben.
-Allerdings gibt es jetzt hier in wenigen Monaten Wahlen in Nordrhein-Westfalen.
-Wie groß ist Ihre Hoffnung, dass aus diesem Ausschuss, aus dieser Ausschussarbeit wirklich etwas Konstruktives für Sie, für die Stadt, für die Opfer herauskommen kann?
-Reker: Also, ich gebe die Hoffnung ja nie auf.
-Aber in dem Ausschuss geht es im Wesentlichen, nach meiner Wahrnehmung, darum, wer schuld ist und nicht darum, weiterzuentwickeln, welche gesellschaftlichen Konsequenzen jetzt aus diesen schrecklichen Vorfällen gezogen werden.
-Küpper: Es geht auch um die Aufarbeitung, aber das scheint ...
-Reker: Es ist ein verschobenes Thema.
-Es wird hier Wahlkampf mit einem schrecklichen Vorfall unserer Stadt gemacht und das kann mir nicht gefallen.
-Küpper: Im Kontext dieser Silvesternacht fiel auch diese, ja, man muss mittlerweile ja fast sagen, berühmte Armlängen-Äußerung, die Sie getätigt haben.
-Was hat Sie diese Diskussion danach darüber – nicht über die Silvesternacht selber, nicht über die Ereignisse, sondern nur um Ihre Äußerung – gelehrt?
-Reker: Dass es einen Grund gibt, warum Politiker vorgefertigte Antworten geben und nicht spontan antworten, so wie ich mir das erhalten will.
-Es hat mich auch gelehrt, nicht darauf zu setzen, dass Zitate wirklich so gebracht werden, wie sie gefallen sind, nämlich als Beispiel.
-Und es hat mich auch nachdenklich gemacht, hinsichtlich der Zielrichtung vieler Journalisten.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Mit Shitstorms werde ich fertig"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Sie haben mal gesagt: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Ich war die mit dem Attentat, dann war ich die mit der Armlänge"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" .
-Das heißt, kann man überhaupt in unserem öffentlichen Raum dann noch ordentliche Debatten führen, wenn das nur so auf Schlagworte verkürzt wird?
-Reker: Ja, das kann man.
-Und man muss es sogar.
-Und das können die Bürgerinnen und Bürger auch von uns erwarten.
-Ich bin da nicht bereit, mich zu lange bei Dingen aufzuhalten, die letztlich nicht zu einem Ergebnis oder zu einem Ziel führen.
-Wir haben hier eine Millionenstadt, die will nicht nur verwaltet, sondern gesteuert werden, die soll nach vornegebracht werden, da darf man dann nicht so viel Sorgen und Zeit verschwenden, wenn Shitstorms kommen – damit werde ich fertig.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Man erwartet von eiener Frau, dass sie Probleme emotionaler begleitet"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Sie hören den Deutschlandfunk, das Interview der Woche, mit Henriette Reker, der Kölner Oberbürgermeisterin.
-Frau Reker, Sie sind jetzt etwa ein Dreivierteljahr im Amt.
-Frau Merkel war die erste Frau im Bundeskanzleramt.
-Hannelore Kraft war die erste Frau in Nordrhein-Westfalen.
-Sie sind die erste Frau an der Spitze einer deutschen Millionenstadt.
-Spielt das überhaupt noch eine Rolle?
-Reker: Vor einem halben Jahr hätte ich noch gesagt: 'Es spielt keine Rolle.
-' Inzwischen glaube ich, dass es doch so ist, dass zu mir noch eine emotionalere Bindung aufgebaut wird von den Kölnerinnen und Kölner als zu einem Mann an der Spitze.
-Küpper: Wie erklären Sie sich das?
-Reker: Ja, vielleicht dadurch, dass ich mich ganz und gar dieser Stadt zuwende und mich auch auf jeden einzelnen Gesprächspartner einstelle, weil es mich wirklich interessiert und weil man von einer Frau eben auch erwartet, dass sie Probleme emotionaler begleitet.
-Wenn Sie sehen, wie oft ich umarmt und geküsst werden, wenn ich durch die Stadt gehe, dann würden Sie sich wundern.
-Küpper: Sie sind nicht nur die erste Frau an der Spitze einer deutschen Millionenstadt, sondern Sie sind auch die erste parteilose Oberbürgermeisterin.
-Was ist so schlecht an Parteien?
-Reker: Es ist gar nichts Schlechtes an Parteien.
-Wir brauchen die Parteien unbedingt.
-Küpper: Aber Sie brauchen keine?
-Reker: Ich brauchte noch nie eine, nein.
-Mir geht es ganz und gar um die Sache, das war immer schon so.
-Mir geht es ganz und gar um Köln.
-Und es gibt keinen roten, grünen oder schwarzen Kreisverkehr, sondern entweder braucht die Stadt einen oder sie braucht ihn nicht.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Die öffentliche Hand ist ganz überwiegend überfordert mit dem Bau von Großprojekten"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Ein Anliegen oder eine Aufgabe der Kommunen – nicht nur der Kommunen, sondern der öffentlichen Hand – sind ja häufig auch Großprojekte.
-Das funktioniert nicht immer gut in Köln, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Oper"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" .
-Aber Köln ist damit ja auch nicht alleine, also, Berlin, Stuttgart 21, die Elbphilharmonie in Hamburg, man könnte die Liste jetzt wahrscheinlich beliebig fortsetzen.
-Was lehrt einen das?
-Reker: Die öffentliche Hand ist, meines Erachtens, ganz überwiegend überfordert mit dem Bau von Großprojekten.
-Wenn das gelingt, dauert es länger und ist auch kostspieliger.
-Das liegt eben an den Vorschriften, die für die öffentliche Hand bestehen und es liegt daran, dass in den Haushalten – und auch das ist in allen Städten sehr vergleichbar – immer wenig Luft ist.
-Und ein Großprojekt eben dann funktioniert, wenn es am Anfang gründlich geplant wird, wenn man viel Geld für die Planung in die Hand nimmt und auch ehrlich berechnet, was wird es kosten, also auch immer einen Zuschlag von 15 oder 20 Prozent für Unvorhergesehenes einkalkuliert.
-Und wenn man dann ehrlich ist zur Politik, dann wird das eine solche Bausumme, die sich dann keiner mehr traut zu beschließen.
-Deswegen wird meist auf dieses Unvorhergesehene verzichtet.
-Und das möchte ich in Köln schon ehrlicher haben in Zukunft.
-Da soll man wissen, was auf einen zukommt.
-Küpper: Frau Reker, dann zum Abschluss.
-Am Jahreswechsel wird wahrscheinlich noch einmal die ganze Welt nach Köln schauen, das hängt naturgemäß damit zusammen, dass das dieses Jahr jetzt mit der Kölner Silvesternacht gestartet ist.
-Wie kann sich die Stadt darauf vorbereiten?
-Reker: Ja, wir werden natürlich die Erfahrungen, die wir aus dem vorigen Jahr mitgenommen haben, in Konzepte für das nächste Jahr bringen und uns genau überlegen, wie man das machen kann.
-Wir haben seitdem ja auch andere Großveranstaltungen erfolgreich durchgeführt – ich denke nur an Cologne Pride, also Christopher Street Day, ich denke an den Karneval.
-Und – ja – ich werden den Polizeipräsidenten einladen, mit mir Silvester zu feiern, dann sitzen wir schon mal zusammen.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>每周采访-260925-Fluchtlingspolitik</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -582,6 +459,127 @@
 insbesondere am Anfang doch recht intransparent war?
 es wurde von allen 27 Mitgliedsstaaten ratifiziert.
 Das hätte man ohne Weiteres zu Beginn der Verhandlungen und nicht erst zwei Jahre später veröffentlichen können.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wird genug getan, diesem Satz, den Herta Müller da ja gesagt hat, den umzusetzen, dem Einhalt zu gebieten, dieser Verrohung teilweise der Diskussion?
+Reker: Der Satz von Herta Müller, dass erst Parolen spazieren gehen und dann Messer – ich sage es mal jetzt sinngemäß –, den zitiere ich oft, weil ich glaube, dass der genau stimmt.
+Und diese politische Kultur der Auseinandersetzung, die führt – davon bin ich zutiefst überzeugt – dazu, dass dann auch es zu solchen Tätlichkeiten kommt.
+Weil man muss sich ja mal vorstellen, es gehört ja eine gewisse Überwindung dazu, jemandem ein Messer irgendwie in den Körper zu stechen.
+Das kommt nicht von selbst und da muss eben ein Hasspotenzial aufgebaut sein, was auch nicht von selbst entsteht.
+Und wenn das immer wieder unterstützt wird durch Parolen, durch Menschen, die die Situation befeuern, um ihre eigenen Interessen zu schüren, um ihr Süppchen kochen zu wollen – ohne eine Alternative allerdings zu haben –, dann wird das gefährlich für uns alle.
+Und deswegen trete ich immer dafür ein, dass wir auch eine angemessene, ruhige, argumentative politische Kultur pflegen.
+Küpper: Was kann man da tun?
+Sie sind Juristin.
+Reichen da Gesetze oder ist das eher eine gesellschaftliche Sache?
+Reker: Es ist eine gesellschaftliche Sache, es ist nicht alles justiziabel, was da passiert, das sehen wir ja an Demonstrationen und an Gewalt in den Demonstrationen.
+Ich glaube, dass man da ganz früh ansetzen muss.
+Und ich glaube auch, dass diese Flüchtlingsbewegung, die jetzt eingetreten sind, eine Chance ist für Kinder, in der Schule sich schon damit zu beschäftigen.
+Das erlebe ich nämlich, dass schon Schulkinder lernen, wo kommen die anderen her, warum sind die da – das ist auch eine Chance.
+Küpper: Dann noch kurz: Das Gericht hat den Attentäter zu 14 Jahren Freiheitsstrafe verurteilt, allerdings niederer Beweggründe dabei verneint, obwohl es ja klar eine rechtsextreme Gewaltbereitschaft damals gab.
+Das ist ein – kann man, glaube ich, so sagen – recht mildes Urteil gewesen.
+Welche Botschaft geht davon aus?
+Reker: Also, ich konnte das nicht nachvollziehen, dass man die niedrigen Beweggründe nicht angenommen hat.
+Ich muss Ihnen sagen, ich finde das jetzt für mich persönlich nicht wichtig, ob der Attentäter zu 14 oder 15 Jahren verurteilt wird.
+Küpper: Aber wir sprechen über die gesellschaftliche ...
+Reker: Also, ich kann einfach nicht nachvollziehen, wie jemand aus rechter Gewalt töten will und das soll kein niedriger Beweggrund sein.
+Und deswegen habe ich auch so eine Sorge vor der Revision, die ich niemals eingelegt hätte.
+Ich stelle mir mir Grausen vor, dass ein Bundesgericht bestätigt, dass man aus rechter Gewalt einen Mordversuch macht und das keine niedrigen Beweggründe sein sollen.
+Ich bin mal sehr gespannt.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es sind viele positive Dinge übrig geblieben von der Silvesternacht"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Sie hören das Interview der Woche im Deutschlandfunk.
+Zu Gast ist Henriette Reker, die Oberbürgermeisterin der Stadt Köln.
+Frau Reker, am Anfang des Jahres, da stand die Silvesternacht – die ist mittlerweile ein geflügeltes Wort, gerade im Kontext von Köln.
+Wie viel von dieser Silvesternacht ist in Ihrer Stadt noch zu spüren?
+Reker: Es ist ganz viel Positives von dieser Silvesternacht zu spüren.
+Küpper: Was?
+Reker: Die Silvesternacht hat mich ja dazu gebracht, ein """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Stärkungsmodell Sicherheit"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" zu konstruieren.
+Eine Zusammenarbeit, eine institutionelle Zusammenarbeit mit der Polizei, die es in dieser Form noch nie gegeben hat in Köln.
+Und es hat auch einen stärkeren Personaleinsatz gegeben für die Polizei, die Stadt hat 100 Ordnungskräfte mehr auf der Straße.
+Es sind viele positive Dinge übrig geblieben von der Silvesternacht.
+Küpper: Das Image hat nicht gelitten?
+Reker: Das Image hat gelitten.
+Aber ich glaube, das Schlimmste daran, an Silvester, war wirklich das Trauma der überfallenen Frauen, dass sicherlich nicht nach wenigen Monaten ausgestanden ist.
+Denen galt auch mein erster Gedanke.
+Aber mitzuweinen hat da wenig Zweck.
+Da geht es darum zu handeln und solche Dinge in der Zukunft zu verhindern.
+Das habe ich getan.
+Küpper: Dennoch muss die Sache auch aufgearbeitet werden, das haben Sie ja auch gerade gesagt.
+Wenn man da auf die juristische Seite guckt, ich habe diese Woche mal beim Amtsgericht nachgefragt, da sind jetzt 15 Urteile gefällt worden.
+Angesichts der Tatsache, der hohen Zahl von Anzeigen – über 1.000 – und Anzahl der jetzt über acht Monate, die verstrichen sind seitdem, wie zufrieden sind Sie mit dem?
+Reker: Gar nicht zufrieden.
+Gar nicht zufrieden.
+Aber das war ja zu erwarten, dass es sehr schwerfallen wird, dass die Frauen dann diese Täter wiedererkennen.
+Also, das geht im Einzelfall, aber ganz überwiegend geht es eben nicht.
+Und das ist daran wirklich schlimm, dass die Männer nicht zur Rechenschaft gezogen werden können.
+Küpper: Das heißt, es war klar, dass diese Erwartungshaltung, die es da ein stückweit gab, automatisch enttäuscht werden musste?
+Reker: Ich habe das befürchtet, ja.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es wird hier Wahlkampf mit einem schrecklichen Vorfall in unserer Stadt gemacht"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Wenn wir auf die politische Aufarbeitung gucken, da gibt es im Düsseldorfer Landtag einen parlamentarischen Untersuchungsausschuss, vor dem Sie ja auch schon als Zeugin ausgesagt haben.
+Allerdings gibt es jetzt hier in wenigen Monaten Wahlen in Nordrhein-Westfalen.
+Wie groß ist Ihre Hoffnung, dass aus diesem Ausschuss, aus dieser Ausschussarbeit wirklich etwas Konstruktives für Sie, für die Stadt, für die Opfer herauskommen kann?
+Reker: Also, ich gebe die Hoffnung ja nie auf.
+Aber in dem Ausschuss geht es im Wesentlichen, nach meiner Wahrnehmung, darum, wer schuld ist und nicht darum, weiterzuentwickeln, welche gesellschaftlichen Konsequenzen jetzt aus diesen schrecklichen Vorfällen gezogen werden.
+Küpper: Es geht auch um die Aufarbeitung, aber das scheint ...
+Reker: Es ist ein verschobenes Thema.
+Es wird hier Wahlkampf mit einem schrecklichen Vorfall unserer Stadt gemacht und das kann mir nicht gefallen.
+Küpper: Im Kontext dieser Silvesternacht fiel auch diese, ja, man muss mittlerweile ja fast sagen, berühmte Armlängen-Äußerung, die Sie getätigt haben.
+Was hat Sie diese Diskussion danach darüber – nicht über die Silvesternacht selber, nicht über die Ereignisse, sondern nur um Ihre Äußerung – gelehrt?
+Reker: Dass es einen Grund gibt, warum Politiker vorgefertigte Antworten geben und nicht spontan antworten, so wie ich mir das erhalten will.
+Es hat mich auch gelehrt, nicht darauf zu setzen, dass Zitate wirklich so gebracht werden, wie sie gefallen sind, nämlich als Beispiel.
+Und es hat mich auch nachdenklich gemacht, hinsichtlich der Zielrichtung vieler Journalisten.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Mit Shitstorms werde ich fertig"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Sie haben mal gesagt: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Ich war die mit dem Attentat, dann war ich die mit der Armlänge"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" .
+Das heißt, kann man überhaupt in unserem öffentlichen Raum dann noch ordentliche Debatten führen, wenn das nur so auf Schlagworte verkürzt wird?
+Reker: Ja, das kann man.
+Und man muss es sogar.
+Und das können die Bürgerinnen und Bürger auch von uns erwarten.
+Ich bin da nicht bereit, mich zu lange bei Dingen aufzuhalten, die letztlich nicht zu einem Ergebnis oder zu einem Ziel führen.
+Wir haben hier eine Millionenstadt, die will nicht nur verwaltet, sondern gesteuert werden, die soll nach vornegebracht werden, da darf man dann nicht so viel Sorgen und Zeit verschwenden, wenn Shitstorms kommen – damit werde ich fertig.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Man erwartet von eiener Frau, dass sie Probleme emotionaler begleitet"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Sie hören den Deutschlandfunk, das Interview der Woche, mit Henriette Reker, der Kölner Oberbürgermeisterin.
+Frau Reker, Sie sind jetzt etwa ein Dreivierteljahr im Amt.
+Frau Merkel war die erste Frau im Bundeskanzleramt.
+Hannelore Kraft war die erste Frau in Nordrhein-Westfalen.
+Sie sind die erste Frau an der Spitze einer deutschen Millionenstadt.
+Spielt das überhaupt noch eine Rolle?
+Reker: Vor einem halben Jahr hätte ich noch gesagt: 'Es spielt keine Rolle.
+' Inzwischen glaube ich, dass es doch so ist, dass zu mir noch eine emotionalere Bindung aufgebaut wird von den Kölnerinnen und Kölner als zu einem Mann an der Spitze.
+Küpper: Wie erklären Sie sich das?
+Reker: Ja, vielleicht dadurch, dass ich mich ganz und gar dieser Stadt zuwende und mich auch auf jeden einzelnen Gesprächspartner einstelle, weil es mich wirklich interessiert und weil man von einer Frau eben auch erwartet, dass sie Probleme emotionaler begleitet.
+Wenn Sie sehen, wie oft ich umarmt und geküsst werden, wenn ich durch die Stadt gehe, dann würden Sie sich wundern.
+Küpper: Sie sind nicht nur die erste Frau an der Spitze einer deutschen Millionenstadt, sondern Sie sind auch die erste parteilose Oberbürgermeisterin.
+Was ist so schlecht an Parteien?
+Reker: Es ist gar nichts Schlechtes an Parteien.
+Wir brauchen die Parteien unbedingt.
+Küpper: Aber Sie brauchen keine?
+Reker: Ich brauchte noch nie eine, nein.
+Mir geht es ganz und gar um die Sache, das war immer schon so.
+Mir geht es ganz und gar um Köln.
+Und es gibt keinen roten, grünen oder schwarzen Kreisverkehr, sondern entweder braucht die Stadt einen oder sie braucht ihn nicht.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Die öffentliche Hand ist ganz überwiegend überfordert mit dem Bau von Großprojekten"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Küpper: Ein Anliegen oder eine Aufgabe der Kommunen – nicht nur der Kommunen, sondern der öffentlichen Hand – sind ja häufig auch Großprojekte.
+Das funktioniert nicht immer gut in Köln, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Oper"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" .
+Aber Köln ist damit ja auch nicht alleine, also, Berlin, Stuttgart 21, die Elbphilharmonie in Hamburg, man könnte die Liste jetzt wahrscheinlich beliebig fortsetzen.
+Was lehrt einen das?
+Reker: Die öffentliche Hand ist, meines Erachtens, ganz überwiegend überfordert mit dem Bau von Großprojekten.
+Wenn das gelingt, dauert es länger und ist auch kostspieliger.
+Das liegt eben an den Vorschriften, die für die öffentliche Hand bestehen und es liegt daran, dass in den Haushalten – und auch das ist in allen Städten sehr vergleichbar – immer wenig Luft ist.
+Und ein Großprojekt eben dann funktioniert, wenn es am Anfang gründlich geplant wird, wenn man viel Geld für die Planung in die Hand nimmt und auch ehrlich berechnet, was wird es kosten, also auch immer einen Zuschlag von 15 oder 20 Prozent für Unvorhergesehenes einkalkuliert.
+Und wenn man dann ehrlich ist zur Politik, dann wird das eine solche Bausumme, die sich dann keiner mehr traut zu beschließen.
+Deswegen wird meist auf dieses Unvorhergesehene verzichtet.
+Und das möchte ich in Köln schon ehrlicher haben in Zukunft.
+Da soll man wissen, was auf einen zukommt.
+Küpper: Frau Reker, dann zum Abschluss.
+Am Jahreswechsel wird wahrscheinlich noch einmal die ganze Welt nach Köln schauen, das hängt naturgemäß damit zusammen, dass das dieses Jahr jetzt mit der Kölner Silvesternacht gestartet ist.
+Wie kann sich die Stadt darauf vorbereiten?
+Reker: Ja, wir werden natürlich die Erfahrungen, die wir aus dem vorigen Jahr mitgenommen haben, in Konzepte für das nächste Jahr bringen und uns genau überlegen, wie man das machen kann.
+Wir haben seitdem ja auch andere Großveranstaltungen erfolgreich durchgeführt – ich denke nur an Cologne Pride, also Christopher Street Day, ich denke an den Karneval.
+Und – ja – ich werden den Polizeipräsidenten einladen, mit mir Silvester zu feiern, dann sitzen wir schon mal zusammen.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Küpper:  das auf Sie verübt wurde, ja ein Stück weit für Merkels Flüchtlingspolitik verantwortlich gemacht – so war es zumindest, so hat der Attentäter das für sich diese Verbindung auch schon einmal herstellt, dieses Wir schaffen das und dieses Attentat dann letztendlich?
+Reker: Aber die Reflektion des Täters ist sowieso für mich völlig schleierhaft.
+Küpper: Wie präsent ist dieses Attentat bei Ihnen noch im Alltag?
+Reker: Es ist jeden Tag präsent.
+Ich leide da nicht drunter, ich habe auch keine Zeit, da lange drüber nachzudenken.
+Küpper: und auch nach der Wahl, bei der Verleihung des Heinrich-Böll-Preises an die Schriftstellerin Herta Müller, da hat diese gesagt:     Wenn Worte, wie 'Volksverräter' und 'Lügenpresse' langegenug spazieren gehen, geht auch mal ein Messer spazieren. Wir erleben es ja in Deutschland immer noch tagtäglich, was für eine teilweise rohe und aufgeheizte Debatte wir führen, sei es in den sogenannten  Sozialen Netzwerken , aber auch anderswo.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,7 +916,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="168" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -928,6 +926,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9CDEAA-89E5-47B2-85FD-C77183BA99D2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="350" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A659F61E-09CD-48C1-B80F-EA0D8573AFCF}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -940,24 +957,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
